--- a/diseases/d128/2005-2009.xlsx
+++ b/diseases/d128/2005-2009.xlsx
@@ -6197,12 +6197,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6241,9 +6241,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6252,68 +6249,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -6340,17 +6351,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6375,12 +6386,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2008-03-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6389,79 +6400,165 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>West Nile virus infection</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN40" t="b">
+        <v>1</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -6523,12 +6620,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -6671,12 +6768,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2008-03-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6819,12 +6916,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -6967,25 +7064,25 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.004679328320790043</v>
+        <v>0</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -7085,12 +7182,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7115,12 +7212,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7166,42 +7263,42 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -7263,25 +7360,25 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>0.004679328320790043</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -7411,12 +7508,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7559,12 +7656,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -7707,12 +7804,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -7855,12 +7952,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -8003,12 +8100,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8151,12 +8248,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8299,12 +8396,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -8447,12 +8544,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -8595,12 +8692,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -8743,12 +8840,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -8891,12 +8988,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -9039,25 +9136,25 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.004590733576730967</v>
+        <v>0</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -9157,12 +9254,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9187,93 +9284,104 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>0.001584623749234686</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -9300,17 +9408,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9335,12 +9443,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -9349,79 +9457,165 @@
       <c r="O60" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.004590733576730967</v>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>West Nile virus infection</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN60" t="b">
+        <v>1</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9677,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -9631,25 +9825,25 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>0.004590733576730967</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -9779,12 +9973,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -9927,25 +10121,25 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>0.004590733576730967</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -10075,12 +10269,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -10223,12 +10417,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -10371,12 +10565,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -10519,12 +10713,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -10667,12 +10861,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -10815,12 +11009,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -10963,12 +11157,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -11111,12 +11305,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -11259,12 +11453,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -11407,12 +11601,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -11555,12 +11749,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -11703,12 +11897,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -11851,12 +12045,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -11999,12 +12193,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-10-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -12147,12 +12341,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-10-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -12232,6 +12426,598 @@
         </is>
       </c>
       <c r="BC79" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -12353,7 +13139,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -12363,7 +13149,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11">
@@ -12383,7 +13169,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -12393,7 +13179,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -12415,7 +13201,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d128/2005-2009.xlsx
+++ b/diseases/d128/2005-2009.xlsx
@@ -6197,12 +6197,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+          <t>SER_CZ_ECDC_WNF_ANNUAL</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+          <t>SER_CZ_ECDC_WNF_ANNUAL</t>
         </is>
       </c>
       <c r="AT39" t="n">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6402,17 +6402,17 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+          <t>SER_CZ_ECDC_WNF_ANNUAL</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+          <t>SER_CZ_ECDC_WNF_ANNUAL</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>SRC_FR_ECDC_ATLAS</t>
+          <t>SRC_CZ_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>country:FR:national</t>
+          <t>country:CZ:national</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+          <t>Czechia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+          <t>SER_CZ_ECDC_WNF_ANNUAL</t>
         </is>
       </c>
       <c r="AT40" t="n">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -6634,9 +6634,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -6645,68 +6642,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -6733,17 +6744,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6768,12 +6779,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2008-03-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6782,79 +6793,165 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>West Nile virus infection</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN42" t="b">
+        <v>1</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -6886,12 +6983,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6916,12 +7013,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -6930,9 +7027,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -6941,68 +7035,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -7029,17 +7137,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -7064,12 +7172,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7078,79 +7186,165 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>West Nile virus infection</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN44" t="b">
+        <v>1</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -7182,12 +7376,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7212,12 +7406,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7226,9 +7420,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7237,68 +7428,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -7325,17 +7530,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7360,93 +7565,179 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>SRC_GR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>West Nile virus infection</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>country:GR:national</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Greece annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN46" t="b">
         <v>1</v>
       </c>
-      <c r="O46" t="n">
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT46" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0.004679328320790043</v>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP46" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
-      <c r="AT46" t="n">
-        <v>0</v>
-      </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -7478,12 +7769,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7508,93 +7799,104 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>0.005036795131581571</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -7621,17 +7923,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7656,93 +7958,179 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>SRC_IT_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>West Nile virus infection</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>country:IT:national</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Italy annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN48" t="b">
+        <v>1</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -7774,12 +8162,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7804,12 +8192,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -7818,9 +8206,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -7829,68 +8214,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -7917,17 +8316,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7952,12 +8351,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -7966,79 +8365,165 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>SRC_PL_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>West Nile virus infection</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>country:PL:national</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN50" t="b">
+        <v>1</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -8070,12 +8555,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8100,93 +8585,104 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>0.009653095733322032</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -8213,17 +8709,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8248,93 +8744,179 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>SRC_RO_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>West Nile virus infection</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>country:RO:national</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Romania annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN52" t="b">
+        <v>1</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -8366,12 +8948,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8396,12 +8978,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -8447,42 +9029,42 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8544,12 +9126,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-03-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -8662,12 +9244,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8692,12 +9274,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -8743,42 +9325,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8840,12 +9422,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -8958,12 +9540,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8988,12 +9570,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -9039,42 +9621,42 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -9136,25 +9718,25 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>0.004679328320790043</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -9254,12 +9836,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9284,104 +9866,93 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0.001584623749234686</v>
+        <v>0</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_WNF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_WNF_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9408,17 +9979,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9443,179 +10014,93 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_WNF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_WNF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>SRC_FR_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>West Nile virus infection</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>country:FR:national</t>
-        </is>
-      </c>
-      <c r="AD60" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG60" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN60" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP60" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr">
-        <is>
-          <t>SER_FR_ECDC_WNF_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV60" t="inlineStr">
-        <is>
-          <t>ecdc_atlas_annual</t>
-        </is>
-      </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -9677,12 +10162,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -9825,25 +10310,25 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0.004590733576730967</v>
+        <v>0</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -9973,12 +10458,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -10121,25 +10606,25 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.004590733576730967</v>
+        <v>0</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -10269,12 +10754,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -10417,12 +10902,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -10565,12 +11050,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -10713,12 +11198,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -10861,12 +11346,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -11009,12 +11494,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -11127,12 +11612,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -11157,12 +11642,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -11171,9 +11656,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11182,68 +11664,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SER_CZ_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>SER_CZ_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -11270,17 +11766,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -11305,12 +11801,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -11319,79 +11815,165 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SER_CZ_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>SER_CZ_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>SRC_CZ_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>West Nile virus infection</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>country:CZ:national</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Czechia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN72" t="b">
+        <v>1</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>SER_CZ_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -11423,12 +12005,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -11453,12 +12035,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -11467,9 +12049,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -11478,68 +12057,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -11566,17 +12159,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11601,12 +12194,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -11615,79 +12208,165 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>SRC_ES_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>West Nile virus infection</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>country:ES:national</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Spain annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN74" t="b">
+        <v>1</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_ES_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -11719,12 +12398,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11749,93 +12428,104 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>0.001584623749234686</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -11862,17 +12552,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -11897,93 +12587,179 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>West Nile virus infection</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN76" t="b">
+        <v>1</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -12015,12 +12791,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -12045,12 +12821,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -12059,9 +12835,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12070,68 +12843,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -12158,17 +12945,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -12193,12 +12980,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -12207,79 +12994,165 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>SRC_GR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>West Nile virus infection</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>country:GR:national</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Greece annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN78" t="b">
+        <v>1</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_GR_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -12341,12 +13214,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -12459,12 +13332,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -12489,93 +13362,104 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>0.03004807165623744</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -12602,17 +13486,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -12637,93 +13521,179 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_IT_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>West Nile virus infection</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:IT:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Italy annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>1</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_IT_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -12755,12 +13725,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -12785,12 +13755,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -12799,9 +13769,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -12810,68 +13777,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -12898,126 +13879,3861 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>SRC_PL_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>West Nile virus infection</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>country:PL:national</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Poland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN83" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>SER_PL_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>2</v>
+      </c>
+      <c r="O84" t="n">
+        <v>2</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0.009719624551314794</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>2</v>
+      </c>
+      <c r="O85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>SRC_RO_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>West Nile virus infection</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>country:RO:national</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Romania annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN85" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>SER_RO_ECDC_WNF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2009-02-01</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2009-02</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0.004590733576730967</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr"/>
+      <c r="AT86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>Hong Kong, China</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>D128</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>West Nile virus</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
         <is>
           <t>西尼罗病毒</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2009-02-01</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2009-02</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr"/>
+      <c r="AT87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2009-03-01</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2009-03</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0.004590733576730967</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr"/>
+      <c r="AT88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2009-03-01</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2009-03</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr"/>
+      <c r="AT89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2009-04-01</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2009-04</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
+      <c r="AT90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2009-04-01</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2009-04</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr"/>
+      <c r="AT91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2009-05-01</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2009-05</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr"/>
+      <c r="AT92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2009-05-01</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2009-05</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2009-06-01</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2009-06</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
+      <c r="AT94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2009-06-01</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2009-06</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2009-07-01</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2009-07</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
+      <c r="AT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2009-07-01</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2009-07</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2009-08-01</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2009-08</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2009-08-01</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2009-08</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
+      <c r="AT99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
+      <c r="AT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
+      <c r="AT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr"/>
+      <c r="AT105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
         <is>
           <t>2009-12-01</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t>2009-12</t>
         </is>
       </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="inlineStr">
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO83" t="inlineStr">
+      <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP83" t="inlineStr">
+      <c r="AP106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR83" t="inlineStr">
+      <c r="AR106" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS83" t="inlineStr"/>
-      <c r="AT83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU83" t="inlineStr">
+      <c r="AS106" t="inlineStr"/>
+      <c r="AT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV83" t="inlineStr">
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr"/>
+      <c r="AT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="AW83" t="inlineStr">
+      <c r="AW107" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
+      <c r="AX107" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="AY83" t="inlineStr">
+      <c r="AY107" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
+      <c r="AZ107" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="BA83" t="inlineStr">
+      <c r="BA107" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="BB83" t="inlineStr">
+      <c r="BB107" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="BC83" t="inlineStr">
+      <c r="BC107" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -13139,7 +17855,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -13149,7 +17865,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>82</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">
@@ -13169,7 +17885,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -13179,7 +17895,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -13201,7 +17917,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
